--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.80340545798045</v>
+        <v>4.193053386921823</v>
       </c>
       <c r="D2" t="n">
-        <v>25.79649404153533</v>
+        <v>4.191930281749491</v>
       </c>
       <c r="E2" t="n">
-        <v>4.090318698067422</v>
+        <v>0.6646767884359561</v>
       </c>
       <c r="F2" t="n">
-        <v>4.171221293954025</v>
+        <v>0.677823460267529</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.59352595987608</v>
+        <v>3.996447968479863</v>
       </c>
       <c r="D3" t="n">
-        <v>24.76186720196547</v>
+        <v>4.023803420319388</v>
       </c>
       <c r="E3" t="n">
-        <v>4.090318698067422</v>
+        <v>0.6646767884359561</v>
       </c>
       <c r="F3" t="n">
-        <v>4.171221293954025</v>
+        <v>0.677823460267529</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.62786816056721</v>
+        <v>5.139528576092172</v>
       </c>
       <c r="D4" t="n">
-        <v>31.8937867511624</v>
+        <v>5.18274034706389</v>
       </c>
       <c r="E4" t="n">
-        <v>4.090318698067422</v>
+        <v>0.6646767884359561</v>
       </c>
       <c r="F4" t="n">
-        <v>4.171221293954025</v>
+        <v>0.677823460267529</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.58088728614511</v>
+        <v>3.344394183998581</v>
       </c>
       <c r="D5" t="n">
-        <v>20.6073415423554</v>
+        <v>3.348693000632752</v>
       </c>
       <c r="E5" t="n">
-        <v>4.090318698067422</v>
+        <v>0.6646767884359561</v>
       </c>
       <c r="F5" t="n">
-        <v>4.171221293954025</v>
+        <v>0.677823460267529</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.78501953602261</v>
+        <v>5.002565674603674</v>
       </c>
       <c r="D6" t="n">
-        <v>30.98798213668412</v>
+        <v>5.03554709721117</v>
       </c>
       <c r="E6" t="n">
-        <v>4.090318698067422</v>
+        <v>0.6646767884359561</v>
       </c>
       <c r="F6" t="n">
-        <v>4.171221293954025</v>
+        <v>0.677823460267529</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
